--- a/astro-site/public/dl/bakery-business-plan/bakery-opening-checklist.xlsx
+++ b/astro-site/public/dl/bakery-business-plan/bakery-opening-checklist.xlsx
@@ -1200,7 +1200,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="104.75" customHeight="1">
+    <row r="13" ht="59.75" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>☐</t>
@@ -1223,11 +1223,11 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Your health department sets what must be displayed (for example a consumer advisory and allergen notice, or ingredient and allergen labels), and the federal and state labor law posters go in a common area. If you serve alcohol, your state liquor license and its posted notices apply: check with your state alcohol agency</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
+          <t>Label packaged and wholesale items with the ingredient list, net contents and the 9 major allergens (FDA); your health department may ask for more</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="104.75" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t>☐</t>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>It is often checked at inspection. Cardboard and organic waste (dough and production scraps); this plan does not fry, so there is no used cooking oil to manage</t>
+          <t>It is often checked at inspection. Cardboard and organic waste (dough and production scraps); this plan does not fry, so there is no used cooking oil to manage. Butter and mixer wash water still reach the drain: ask whether you need a grease interceptor where the local plumbing code requires it</t>
         </is>
       </c>
     </row>
